--- a/feedback_surveys/012_individual_impact_on_marine_environment--feedback_surveys.xlsx
+++ b/feedback_surveys/012_individual_impact_on_marine_environment--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1351,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -1435,46 +1435,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>marine_protected_areas</t>
+          <t>other_marine_activities</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Marine protected areas</t>
+          <t>Other marine activities</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ocean_habits_choices</t>
+          <t>sustainability_ideas_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>other_marine_activities</t>
+          <t>adopt_a_sustainable_lifestyle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Other marine activities</t>
+          <t>Adopt a sustainable lifestyle</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ocean_habits_choices</t>
+          <t>sustainability_ideas_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>other_marine_activities</t>
+          <t>educate_others</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Other marine activities</t>
+          <t>Educate others</t>
         </is>
       </c>
     </row>
@@ -1486,46 +1486,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>adopt_a_sustainable_lifestyle</t>
+          <t>support_marine_conservation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Adopt a sustainable lifestyle</t>
+          <t>Support marine conservation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sustainability_ideas_choices</t>
+          <t>marine_habits_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>educate_others</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Educate others</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sustainability_ideas_choices</t>
+          <t>marine_habits_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>support_marine_conservation</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Support marine conservation</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>often</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1554,46 +1554,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>marine_habits_frequency_choices</t>
+          <t>marine_environmental_protection_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>marine_habits_frequency_choices</t>
+          <t>marine_environmental_protection_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Somewhat agree</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>strongly_agree</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Strongly agree</t>
+          <t>Neither agree nor disagree</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>somewhat_agree</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Somewhat agree</t>
+          <t>Somewhat disagree</t>
         </is>
       </c>
     </row>
@@ -1639,44 +1639,10 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>neither_agree_nor_disagree</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
-        <is>
-          <t>Neither agree nor disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>marine_environmental_protection_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>somewhat_disagree</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Somewhat disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>marine_environmental_protection_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>strongly_disagree</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>Strongly disagree</t>
         </is>
